--- a/templates/Strukturvorlage_DataDictionary_KBOB_FM_v1.0.0_validated2026-08-06.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_KBOB_FM_v1.0.0_validated2026-08-06.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="435" yWindow="225" windowWidth="27825" windowHeight="14640" tabRatio="525" firstSheet="4" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Impressum" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Header" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dictionary_public" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Classes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Properties" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Values" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Documents" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="GroupOfProperties" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Data_Template" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gelöschte Bauteile" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="Rules" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impressum" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Header" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary_public" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Values" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GroupOfProperties" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Template" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gelöschte Bauteile" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
-    <externalReference r:id="rId15"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
   </externalReferences>
   <definedNames>
     <definedName name="Affectation_de_classe">Rules!$C$2:$C$47</definedName>
@@ -1602,8 +1602,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Impressum"/>
       <sheetName val="Anleitung"/>
@@ -2138,8 +2138,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Anleitung"/>
       <sheetName val="Header"/>
@@ -2350,8 +2350,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Impressum"/>
       <sheetName val="Anleitung"/>
@@ -3530,7 +3530,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="26.140625" customWidth="1" style="234" min="1" max="1"/>
-    <col width="1.7109375" customWidth="1" style="234" min="2" max="2"/>
+    <col width="28" customWidth="1" style="234" min="2" max="2"/>
     <col width="31.7109375" bestFit="1" customWidth="1" style="234" min="3" max="3"/>
     <col width="1.7109375" customWidth="1" style="234" min="4" max="4"/>
     <col width="18.28515625" customWidth="1" style="234" min="5" max="5"/>
@@ -3552,7 +3552,11 @@
   <sheetData>
     <row r="1" ht="17.65" customHeight="1" s="234">
       <c r="A1" s="163" t="n"/>
-      <c r="B1" s="163" t="n"/>
+      <c r="B1" s="34" t="inlineStr">
+        <is>
+          <t>Data Templates</t>
+        </is>
+      </c>
       <c r="C1" s="34" t="inlineStr">
         <is>
           <t>GoP</t>
@@ -3700,7 +3704,11 @@
     </row>
     <row r="2" ht="163.5" customHeight="1" s="234">
       <c r="A2" s="163" t="n"/>
-      <c r="B2" s="163" t="n"/>
+      <c r="B2" s="76" t="inlineStr">
+        <is>
+          <t>DataTemplate-ID</t>
+        </is>
+      </c>
       <c r="C2" s="76" t="inlineStr">
         <is>
           <t>GoP - Designation/Bezeichnung/Désignation/Designazione</t>
@@ -4304,7 +4312,11 @@
           <t>Classes</t>
         </is>
       </c>
-      <c r="B3" s="75" t="n"/>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Stable identity</t>
+        </is>
+      </c>
       <c r="C3" s="163" t="n"/>
       <c r="D3" s="75" t="n"/>
       <c r="E3" s="163" t="n"/>
@@ -4436,7 +4448,11 @@
           <t>Class - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
-      <c r="B4" s="164" t="n"/>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Repeat the same ID across rows to attach 0..n GroupOfProperties</t>
+        </is>
+      </c>
       <c r="C4" s="165" t="n"/>
       <c r="D4" s="164" t="n"/>
       <c r="E4" s="165" t="n"/>
@@ -4568,6 +4584,11 @@
           <t>Grundstück</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>KBOB_Identifikation</t>
@@ -4740,6 +4761,11 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>Grundstück</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4908,6 +4934,11 @@
           <t>Grundstück</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>KBOB_Nutzung</t>
@@ -5056,6 +5087,11 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>Grundstück</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5348,6 +5384,11 @@
           <t>Gebäude</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>KBOB_Identifikation</t>
@@ -5528,6 +5569,11 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>Gebäude</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5694,6 +5740,11 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>Gebäude</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5846,6 +5897,11 @@
           <t>Gebäude</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>KBOB_Compliance</t>
@@ -6004,6 +6060,11 @@
           <t>Gebäude</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>KBOB_Geometrie</t>
@@ -6160,6 +6221,11 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>Gebäude</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6311,6 +6377,11 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>Gebäude</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6609,6 +6680,11 @@
           <t>Geschoss</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>KBOB_Identifikation</t>
@@ -6768,6 +6844,11 @@
           <t>Geschoss</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>KBOB_Klassifikation</t>
@@ -6917,6 +6998,11 @@
       <c r="A20" t="inlineStr">
         <is>
           <t>Geschoss</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7223,6 +7309,11 @@
           <t>Raum</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>KBOB_Identifikation</t>
@@ -7392,6 +7483,11 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>Raum</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7549,6 +7645,11 @@
           <t>Raum</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>KBOB_Nutzung</t>
@@ -7714,6 +7815,11 @@
       <c r="A25" t="inlineStr">
         <is>
           <t>Raum</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7909,6 +8015,11 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>Raum</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8108,6 +8219,11 @@
       <c r="A27" t="inlineStr">
         <is>
           <t>Raum</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8406,7 +8522,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B29" s="81" t="n"/>
+      <c r="B29" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>KBOB_Identifikation</t>
@@ -8586,7 +8706,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B30" s="81" t="n"/>
+      <c r="B30" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>KBOB_Klassifikation</t>
@@ -8752,6 +8876,11 @@
       <c r="A31" s="43" t="inlineStr">
         <is>
           <t>Bauteil</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8905,7 +9034,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B32" s="81" t="n"/>
+      <c r="B32" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C32" s="98" t="inlineStr">
         <is>
           <t>KBOB_Compliance</t>
@@ -9061,7 +9194,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B33" s="81" t="n"/>
+      <c r="B33" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C33" s="98" t="inlineStr">
         <is>
           <t>KBOB_Geometrie</t>
@@ -9213,7 +9350,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B34" s="81" t="n"/>
+      <c r="B34" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>KBOB_Technik</t>
@@ -9373,7 +9514,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B35" s="81" t="n"/>
+      <c r="B35" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C35" s="98" t="inlineStr">
         <is>
           <t>KBOB_Wartung</t>
@@ -9549,7 +9694,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B36" s="81" t="n"/>
+      <c r="B36" s="81" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C36" s="98" t="inlineStr">
         <is>
           <t>KBOB_Material</t>
@@ -20188,7 +20337,7 @@
       </c>
       <c r="B6" s="161" t="inlineStr">
         <is>
-          <t>KBOB FM Data Dictionary</t>
+          <t>KBOB Data Dictionary FM</t>
         </is>
       </c>
       <c r="C6" s="180" t="inlineStr">
@@ -20210,7 +20359,7 @@
       </c>
       <c r="B7" s="161" t="inlineStr">
         <is>
-          <t>KBOB Datenkatalog FM</t>
+          <t>KBOB Data Dictionary FM</t>
         </is>
       </c>
       <c r="C7" s="180" t="inlineStr">
@@ -20232,7 +20381,7 @@
       </c>
       <c r="B8" s="161" t="inlineStr">
         <is>
-          <t>Catalogue de données KBOB FM</t>
+          <t>KBOB Data Dictionary FM</t>
         </is>
       </c>
       <c r="C8" s="180" t="inlineStr">
